--- a/tame_output/ON/bt/strategyON_20231024.xlsx
+++ b/tame_output/ON/bt/strategyON_20231024.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-22</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>83.1%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-22</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -901,26 +901,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,12 +929,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-22</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>100.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-22</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-22</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.8%</t>
+          <t>-157.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.7%</t>
+          <t>130.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-22</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1759"/>
+  <dimension ref="A1:G1760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41967,7 +41967,7 @@
         <v>45221</v>
       </c>
       <c r="B1759" t="n">
-        <v>2.930344769383407</v>
+        <v>2.940632196767551</v>
       </c>
       <c r="C1759" t="n">
         <v>2.964689051375926</v>
@@ -41983,6 +41983,29 @@
       </c>
       <c r="G1759" t="n">
         <v>4.259070616478141</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="2" t="n">
+        <v>45222</v>
+      </c>
+      <c r="B1760" t="n">
+        <v>3.066950654063524</v>
+      </c>
+      <c r="C1760" t="n">
+        <v>2.992474709334104</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>1.518617014984511</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>3.599565091014161</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>2.157302608503688</v>
+      </c>
+      <c r="G1760" t="n">
+        <v>4.286856274436318</v>
       </c>
     </row>
   </sheetData>
